--- a/cedulas_Procesadas.xlsx
+++ b/cedulas_Procesadas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ContratosSuperflex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE319EE-CAC3-45DA-B2EF-E00ED3DC19E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726F518B-0B61-4DBD-9A4D-471DCF4E68C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25680" yWindow="11100" windowWidth="12150" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>VILLAVICENCIO 1</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>18/02//2026 10:00pm</t>
+  </si>
+  <si>
+    <t>11:53am 7/03/2026</t>
   </si>
 </sst>
 </file>
@@ -671,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2578"/>
+  <dimension ref="A1:F2602"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.85546875" customWidth="1"/>
@@ -13548,6 +13551,111 @@
     <row r="2578" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2578" s="5">
         <v>800159687</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2581" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2582" s="5">
+        <v>1234788097</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2583" s="3">
+        <v>1122646404</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2584" s="5">
+        <v>1006794764</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2585" s="5">
+        <v>1006719691</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2586">
+        <v>68297670</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2587" s="3">
+        <v>40440484</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2588" s="3">
+        <v>40442222</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2589">
+        <v>80450866</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2590">
+        <v>80155489</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2591">
+        <v>800159687</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2592">
+        <v>1022925236</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2594" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2595" s="5">
+        <v>1234788097</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2596" s="5">
+        <v>1006794764</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2597" s="3">
+        <v>1006719691</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2598" s="5">
+        <v>68297670</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2599" s="3">
+        <v>80450866</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2600" s="5">
+        <v>80155489</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2601" s="5">
+        <v>800159687</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2602" s="3">
+        <v>1022925236</v>
       </c>
     </row>
   </sheetData>
